--- a/sasmazer-web-data.xlsx
+++ b/sasmazer-web-data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izzet\Desktop\site-paketi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\claude-site\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7849722-EA79-4029-B113-72BF23D53E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{793C5978-9067-4742-8D75-3569BB73C480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{01CF4AA5-8AA0-4432-B568-E754E4675557}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WEB_EXPORT_PRODUCTS" sheetId="1" r:id="rId1"/>
@@ -25,31 +25,13 @@
     <definedName name="UrunListesi">#REF!</definedName>
     <definedName name="UrunSecimListesi">[1]PP!$B$2:$B$1100</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3517" uniqueCount="1148">
   <si>
     <t>sap_kodu</t>
   </si>
@@ -3318,12 +3300,6 @@
     <t>Beyaz eşya / klima + dondurucu kampanyası</t>
   </si>
   <si>
-    <t>457000010100|457100000011|457100000015|457100000019|457100000020|457100000035|7115421400|7131960100|7175722600|7175750900|7175751100|7178526000|7184270110|7184270120|7184270140|7184270150|7188220190|7188270140|7188270150|7188270160|7188270170|7188270180|7262420181|7263520113|7263520116|7281620154|7281620161|7281620197|7282120192|7283120197|7285420143|7285520143|7286520155|7286520182|7287220188|7289120118|7289120155|7289120196|7291620136|7296520137|7296520147|7296520186|7296529446|7606610177|7607310177|7607510177|7622810177|7629710177|7630110177|7630610177|7631710177|7631810177|7632310177|7632710177|7633010177|7633610177|7633710177|7633810177|7633910177|7634610177|7671710177|7673310177|7675410177|8505581100|8510851100|8511191100|8808751100|8866251100|8866271100|8896391100|9207931100|9208011100|9212751100|9212771100|9212791100|9212811100|9212831100|9212851100|9212871100|9212891100|9215521100|9217341100|9260571100|9260591100|9200301100|9209341100|9209361100|9209721100|7184270100|7289120114|7631910177|7632010177|9209681100|9209701100|457000009600|457100000013|457100000014|457100000023|457100000024|457100007200|457100034700|7170520100|7178042900|7184170110|7184270190|7184270230|7281620116|7281620117|7281620118|7282120136|7282120137|7283120185|7289120117|7289120157|7289120164|7289120188|7291727736|7293420156|7293720177|7295520135|7295520166|7299420123|7632110177|7632210177|7634710177|7634810177|7634910177|7635210177|8896331100|8896351100|8896371100|9200321100|9200341100|9200361100|9205831100|9212261100</t>
-  </si>
-  <si>
-    <t>1280 YKMP IG|10120 MX|10120 MXS|9120 DMXS|9120 DMX|8100 MX|9120 MP O|9120 MP OG|1280 YKM|9140 MP OG|10140 MP OG|10140 MP O|1001 KMX|901 KMX|931 KMP IG|1011 KMP IG|911 KMP IG|1100 KMX|901 KMP I|901 KMX S|1001 KMX S|901 KMP IG|574561 EI|574508 MB|574509 MB|274532 MB|278550 EB FİT|274532 EI|274580 EDI|583630 EI|583630 EB|391641 EI|278551 EGC AI Fit|278551 EBC AI Fit|284630 EI|583629 EB|578557 EI Fit|583650 EI|278551 ESC AI Fit|283613 EI|283613 EB|283616 EI|283616 IEBI|9252 MI|Z9463 FCB|Z9463 FCG TEZGAHALTI|Z 6166 SC|6433|6444|AB 240|6444 OK|6444 OK I|6455 WF MG|6444 WF|AB 262|6667 WF I|6467 WF SC|6467 WF I|6467 WF|6567 WF I|ABC 160 G TEZGAHALTI|ABM 181 D TEZGAHALTI|6167 SC|48726 MONOFAZE INVERTER|34726 MONOFAZE INVERTER|12220 P - PORTATİF (Sadece Soğutma)|15325 (WiFi Opsiyonel)|24325  (WiFi Opsiyonel)|18325 (WiFi Opsiyonel)|24465 HP|12770 AL WiFi|12670 WiFi|09570 HP WiFi|12570 HP WiFi|18570 HP WiFi|24570 HP WiFi|09470 HP WiFi|12470 HP WiFi|18470 HP WiFi|24470 HP WiFi|26326 MONOFAZE INVERTER|55726 MONOFAZE INVERTER|18605|24605|09560 HP|12325 A (WiFi Opsiyonel)|09325 A (WiFi Opsiyonel)|15325 S (Sadece Soğutma)|1101 KMX|583628 EB|6444 OK A|6688 DI|09605|12605|1070 YKMX I|11140 MXA|11140 MX|12140 MX|12140 MXA|9100 DMX|9120 TMX|10120 IMP|1011 KMP I|1002 KMP HA|1201 KMX|578556 EB|274533 MB|274532 EB|278551 EDI|278551 ESC|583628 EI|583625 IEB Fit|583632 EB Fit|583632 EI Fit|578557 EB Fit|574509 MI|383510 EI|391572 EI|391572 ESC|391572 EB|391572 ESS|6455 WF I|6455 WF|6567 WF|ABM 152 D|ABC 152 G|6466|09465 HP|12465 HP|18465 HP|12560 HP|18560 HP|24560 HP|07325 A|21325 T (WiFi Opsiyonel)</t>
-  </si>
-  <si>
     <t>457294940111|457500000028|457500000030|457500000033|457500000156|457510920030|457514320038|457515020040|457515020043|457515220031|457520920005|457521020006|7217620110|7223320110|7254140100|7254140101|7266920110|7278420100|7278420112|7278420113|7278420192|7278440110|7283640817|7284740110|7285940110|7294220110|7294220112|7294220114|7294220115|7294220190|7294220191|7294220192|7294940110|7502720034|7510920030|7514320038|7515020040|7515020043|7515220031|7520920005|7521020006|7285920110|457200000021|457200000022|457294940110|457500000040|457500000041|457500000044|457500000152|457500000155|457500000159|7217620111|7223320111|7254120590|7251040410|7254120110|7278420010|7278420190|7279720011|7294220194|7294920110|7294920116</t>
   </si>
   <si>
@@ -3343,18 +3319,182 @@
   </si>
   <si>
     <t>OCAK|DAVLUMBAZ</t>
+  </si>
+  <si>
+    <t>TV_TKM</t>
+  </si>
+  <si>
+    <t>55 inç üzeri TV + KEA kampanyası</t>
+  </si>
+  <si>
+    <t>EH7T00|GF2T00|EH8T00|GF3T00|EH9T00|GF4T00|AR6T00|AR5T00|AR4T00|EV1T00|GZ6T00|EV2T00|GZ7T00|EV3T00|HG3T00|AT5T00|AT4T00|AT3T00|FA5T00|HC7T00|FA6T00|HC9T00|FU7T00|HD2T00|CE2T00|CD7T00|DP7T00|CD5T00|DP6T00|DR2T00|GX6T00|DR4T00|GY4T00|CV7T00|GX3T00|CV8T00|GX4T00|CS2T00|CS3T00|AR2T00|AR3T00|GH7T00|GL4T00|GW1T00|AT2T00|AT3T00|CD4T00|EA2T00|BJ8T00|BJ4T00|BJ5T00|BJ7T00|CY5T00|EA1T00|FU7T00|GV1T00|GV3T00|GZ5T00|GZ7T00|HG3T00|HC7T00|HC9T00|HD2T00</t>
+  </si>
+  <si>
+    <t>7489770111|7489770132|7489770136|7489770133|8918601100|8811521100|8917001100|8818941100|8819031100|8818931100|8916541100|8912221100|8815551100|8815561100|8818131100|8916531100|8918041100|8916191100|8917361100|8912241100|8818151100|7489570101|7489570111|8911231100|8818501100|8838261100|8839981100|9009081100|8916061100|8918221100|8919661100|9009071100|8815861100|8915591100|8814161100|8913201100|8918631100|8918941100|8916981100|8817721100|8817731100|8919521100|8919541100|8916521100|8818041100|8919511100|8914711100|8818031100|7489770138|7489770140|7489770141|9250411100|8818051100|8919531100|7464000101|8914811100|7460010100|7460020100|7489470101|7489470102|7489470100|7489470107|7489470103|7489470116|8819981100|8917981100|8919771100|7489970102|8912971100|8918991100|7460010101|7460010102|7462000100|8819041100|8914761100|8914721100|8918291100|8837651100|8919121100|8834421100|8817321100|8917621100|8817311100|8910861100|8913671100|8904520100|9242391600|8813101100|8916011100|8911641100|8919431100|8813081100|8919051100|8912851100|8918391100|9249571600|8915951100|8914131100|8918421100|8914111100|8915141100|9242441600|8835771100|8918381100|8910401100|8911061100|8915441100|8816611100|8918981100|8918411100|8910661100|990427100088|8915071100|8919451100|9245551600|9245561600|8915681100|8917511100|8915081100|8919461100|8918441100|8870671600|8870491600|8870861600|8870871600|8870881600|8871001600</t>
+  </si>
+  <si>
+    <t>SUPURGE_TKM</t>
+  </si>
+  <si>
+    <t>Süpürge + TKM kampanyası</t>
+  </si>
+  <si>
+    <t>990427100088</t>
+  </si>
+  <si>
+    <t>7465000100|7465000101|7465000102</t>
+  </si>
+  <si>
+    <t>BE_ELEKTRONIK</t>
+  </si>
+  <si>
+    <t>Beyaz eşya + elektronik kampanyası</t>
+  </si>
+  <si>
+    <t>457000010100|457100000011|457100000015|457100000019|457100000020|457100000035|457500000030|457500000033|457500000156|457510920030|457514320038|457515020040|457515020043|457515220031|457520920005|457521020006|7175722600|7184270110|7184270120|7184270140|7184270150|7188220190|7188270140|7188270150|7188270160|7188270170|7188270180|7262420181|7263520116|7281620161|7281620197|7282120185|7283120197|7285420143|7285520143|7286520155|7286520182|7287220188|7289120155|7291620136|7296520137|7296520147|7296520186|7296529446|7606610177|7629710177|7630110177|7630610177|7631710177|7631810177|7631910177|7632010177|7632310177|7632710177|7633010177|7633610177|7633710177|7633810177|7633910177|7634610177|7634810177|7634910177|7635210177|9212751100|9212771100|9212791100|9212811100|9212831100|9212851100|9212871100|9212891100|9215521100|9217341100|8505581100|8510851100|8511191100|8896331100|8896351100|8896371100|8896391100</t>
+  </si>
+  <si>
+    <t>9249281600|9247901600|9245681600|9247891600|9245671600|9248871600|9248881600</t>
+  </si>
+  <si>
+    <t>KLIMA_FIXPACK7000</t>
+  </si>
+  <si>
+    <t>Klima + Fixpack 7.000 TL kampanyası</t>
+  </si>
+  <si>
+    <t>9212751100|9212771100|9212791100|9212811100|9212831100|9212851100|9212871100|9212891100|9200301100|9200321100|9200341100|9200361100|8896331100|8896351100|8896371100|8896391100|9215521100|8510851100|8505581100|9217341100|8511191100</t>
+  </si>
+  <si>
+    <t>9244741600</t>
+  </si>
+  <si>
+    <t>KLIMA_FIXPACK2000</t>
+  </si>
+  <si>
+    <t>Klima + Fixpack 2.000 TL kampanyası</t>
+  </si>
+  <si>
+    <t>AKILLI_SAAT_TKM</t>
+  </si>
+  <si>
+    <t>Akıllı saat + TKM kampanyası</t>
+  </si>
+  <si>
+    <t>9243431600|9243441600</t>
+  </si>
+  <si>
+    <t>7489470101|7489470102|7489470100|7489470107|7489470103|7489470116</t>
+  </si>
+  <si>
+    <t>ANK_SET_DONDURUCU</t>
+  </si>
+  <si>
+    <t>Seçili ankastre set + dondurucu kampanyası</t>
+  </si>
+  <si>
+    <t>7757783011|7718186374|7768280106|7779320240|7779420287|7779420288|7779420289|7779420292|7763680120|7763680121|7763680122|7763680130|7763680131|7763680132|7763680140|7757180110|7757189027|7763680144|7763680145|7763680146|7703330101|7704330102|7704330103|7704330106|7704330118|7704330122|7704330123|7704331102|7704331103|7704331104|7704331217|7705330103|7705330110|7705330111|7705331101|7705331102</t>
+  </si>
+  <si>
+    <t>457294940111|457500000028|457500000030|457500000033|457500000156|457510920030|457514320038|457515020040|457515020043|457515220031|457520920005|457521020006|7217620110|7223320110|7254140100|7254140101|7266920110|7278420100|7278420112|7278420113|7278420192|7278440110|7283640817|7284740110|7285940110|7294220110|7294220112|7294220114|7294220115|7294220190|7294220191|7294220192|7294940110|7502720034|7510920030|7514320038|7515020040|7515020043|7515220031|7520920005|7521020006|7285920110</t>
+  </si>
+  <si>
+    <t>DEGISIM_15000</t>
+  </si>
+  <si>
+    <t>Değişim kampanyası - Ankastre set 15.000 TL</t>
+  </si>
+  <si>
+    <t>7768270162|7768270195|7768270165|7768270161|7768270213|7768270188|7768270211|7768270137|7768270138|7768270136|7768270168|7768270146|7768270151|7768270160|7768270224|7768270232|7768270190|7768280120|7779420294|7768270185|7768280121|7768270204|7769470112|7768270163|7768270171|7768270167|7768270164|7779420296|7768280102|7768280101|7768280104|7768280103|7768270178|7768270202|7768270201|7768270203|7768270183|7779320235|7779320232|7779320234|7757880103|7757783011|7718186374|859991734750|859991734730|7768270243|7779420287|7779420289|7779420288|7779420292|7779320240|7768280106|7791686708|7791686709|7768270196|7762770103|7756388608|7762670102|7762780103|8770671100|8770741100|8770751100|7763680144|7763680145|7763680146|7763680132|7763680130|7763680131|7785070161|7763680101|7763680102|7763680103|7763680148|7763680149|7763680150|7763680120|7763680121|7763680122|7763680140|7763670153|7763670160|7763670152|7763670175|7763670148|7783270120|7768870116|7784570113|7784670112|7763580126|7763680124|7763580115|7763680125|7763570201|8770661100|8770811100|7724070105|7725570104|7763670150|7763670163|7763670167|7763670154|7763670158|7763670180|7763680114|7763580125|7763580114|7763670155|7724070107|7763670177|7763680110|7763680111|7757180110|7757189027|9210511100|9210521100|9210531100|9202141100|8808861100|8808871100|9217831100|9217841100|8862281100|9210871100|7706330103|9210491100|9210501100|7704330114|7704330113|7704330115|7704331106|7704331110|7704330108|7705330101|7704330232|7704330233|7704330120|7704330234|7704330117|7704330124|7704330116|7704331224|7704331272|7704331223|7704330112|7704330127|7704331103|7704331104|7704331102|7704330122|7704330123|7704330106|7704330118|7705331102|7705331101|7705330110|7705330111|7704331117|7705331116|7704331267|7704330103|7704331217|7704330102|7705330103|7703321101|7703330101|7706330102|8863321100|8863341100|9218011100|7704330121|7704331224|9218831100|7703330101|7706330103|7704330112</t>
+  </si>
+  <si>
+    <t>ESKİ ÜRÜN TESLİM ŞARTI VAR</t>
+  </si>
+  <si>
+    <t>DEGISIM_20000</t>
+  </si>
+  <si>
+    <t>Değişim kampanyası - Ankastre set 20.000 TL (İndüksiyon)</t>
+  </si>
+  <si>
+    <t>7768270162|7768270195|7768270165|7768270161|7768270213|7768270188|7768270211|7768270137|7768270138|7768270136|7768270168|7768270146|7768270151|7768270160|7768270224|7768270232|7768270190|7768280120|7779420294|7768270185|7768280121|7768270204|7769470112|7768270163|7768270171|7768270167|7768270164|7779420296|7768280102|7768280101|7768280104|7768280103|7768270178|7768270202|7768270201|7768270203|7768270183|7779320235|7779320232|7779320234|7757880103|7757783011|7718186374|859991734750|859991734730|7768270243|7779420287|7779420289|7779420288|7779420292|7779320240|7768280106|7791686708|7791686709|7768270196|7757180110|7757189027|7757180103|7757187692|9210511100|9210521100|9210531100|9202141100|8808861100|8808871100|9217831100|9217841100|8862281100|9210871100|7706330103|9210491100|9210501100|7704330114|7704330113|7704330115|7704331106|7704331110|7704330108|7705330101|7704330232|7704330233|7704330120|7704330234|7704330117|7704330124|7704330116|7704331224|7704331272|7704331223|7704330112|7704330127|7704331103|7704331104|7704331102|7704330122|7704330123|7704330106|7704330118|7705331102|7705331101|7705330110|7705330111|7704331117|7705331116|7704331267|7704330103|7704331217|7704330102|7705330103|7703321101|7703330101|7706330102|8863321100|8863341100|9218011100|7704330121|7704331224|9218831100|7703330101|7706330103|7704330112</t>
+  </si>
+  <si>
+    <t>TKM_FIXPACK</t>
+  </si>
+  <si>
+    <t>TKM + Fixpack kampanyası</t>
+  </si>
+  <si>
+    <t>7489470100|7489470101|7489470102|7489470116|7489470107|7489470103</t>
+  </si>
+  <si>
+    <t>9244651600|9244661600|9244671600</t>
+  </si>
+  <si>
+    <t>ESPRESSO_FIXPACK</t>
+  </si>
+  <si>
+    <t>Tam otomatik espresso + Fixpack 7.300 TL</t>
+  </si>
+  <si>
+    <t>8914721100</t>
+  </si>
+  <si>
+    <t>SUPURGE_FIXPACK3000</t>
+  </si>
+  <si>
+    <t>TSZ 6282 Süpürge + Fixpack 3.000 TL</t>
+  </si>
+  <si>
+    <t>8914131100</t>
+  </si>
+  <si>
+    <t>9245741600|9245751600|9245761600</t>
+  </si>
+  <si>
+    <t>SUPURGE_FIXPACK1500</t>
+  </si>
+  <si>
+    <t>Seçili süpürge + Fixpack 1.500 TL</t>
+  </si>
+  <si>
+    <t>8910401100|8919431100|8918421100</t>
+  </si>
+  <si>
+    <t>CAYCI_FIXPACK</t>
+  </si>
+  <si>
+    <t>CM 3626 Çay makinesi + Fixpack 500 TL</t>
+  </si>
+  <si>
+    <t>8919961100</t>
+  </si>
+  <si>
+    <t>1280 YKMP IG|10120 MX|10120 MXS|9120 DMXS|9120 DMX|8100 MX|9120 MP O|9120 MP OG|1280 YKM|9140 MP OG|10140 MP OG|10140 MP O|1001 KMX|901 KMX|931 KMP IG|1011 KMP IG|911 KMP IG|1100 KMX|901 KMP I|901 KMX S|1001 KMX S|901 KMP IG|574561 EI|574508 MB|574509 MB|274532 MB|278550 EB FİT|274532 EI|274580 EDI|583630 EI|583630 EB|391641 EI|278551 EGC AI Fit|278551 EBC AI Fit|284630 EI|583629 EB|578557 EI Fit|583650 EI|278551 ESC AI Fit|283613 EI|283613 EB|283616 EI|283616 IEBI|9252 MI|Z9463 FCB|Z9463 FCG TEZGAHALTI|Z 6166 SC|6433|6444|AB 240|6444 OK|6444 OK I|6455 WF MG|6444 WF|AB 262|6667 WF I|6467 WF SC|6467 WF I|6467 WF|6567 WF I|ABC 160 G TEZGAHALTI|ABM 181 D TEZGAHALTI|6167 SC|48726 MONOFAZE INVERTER|34726 MONOFAZE INVERTER|12220 P - PORTATİF (Sadece Soğutma)|15325 (WiFi Opsiyonel)|24325  (WiFi Opsiyonel)|18325 (WiFi Opsiyonel)|24465 HP|12770 AL WiFi|12670 WiFi|09570 HP WiFi|12570 HP WiFi|18570 HP WiFi|24570 HP WiFi|09470 HP WiFi|12470 HP WiFi|18470 HP WiFi|24470 HP WiFi|26326 MONOFAZE INVERTER|55726 MONOFAZE INVERTER|18605|24605|09560 HP|12325 A (WiFi Opsiyonel)|09325 A (WiFi Opsiyonel)|15325 S (Sadece Soğutma)|1101 KMX|583628 EB|6444 OK A|6688 DI|09605|12605|1070 YKMX I|11140 MXA|11140 MX|12140 MX|12140 MXA|9100 DMX|9120 TMX|10120 IMP|1011 KMP I|1002 KMP HA|1201 KMX|578556 EB|274533 MB|274532 EB|278551 EDI|278551 ESC|583628 EI|583625 IEB Fit|583632 EB Fit|583632 EI Fit|578557 EB Fit|574509 MI|383510 EI|391572 EI|391572 ESC|391572 EB|391572 ESS|6455 WF I|6455 WF|6567 WF|ABM 152 D|ABC 152 G|6466|09465 HP|12465 HP|18465 HP|12560 HP|18560 HP|24560 HP|07325 A|21325 T (WiFi Opsiyonel)|278550 EI Fit</t>
+  </si>
+  <si>
+    <t>457000010100|457100000011|457100000015|457100000019|457100000020|457100000035|7115421400|7131960100|7175722600|7175750900|7175751100|7178526000|7184270110|7184270120|7184270140|7184270150|7188220190|7188270140|7188270150|7188270160|7188270170|7188270180|7262420181|7263520113|7263520116|7281620154|7281620161|7281620197|7282120192|7283120197|7285420143|7285520143|7286520155|7286520182|7287220188|7289120118|7289120155|7289120196|7291620136|7296520137|7296520147|7296520186|7296529446|7606610177|7607310177|7607510177|7622810177|7629710177|7630110177|7630610177|7631710177|7631810177|7632310177|7632710177|7633010177|7633610177|7633710177|7633810177|7633910177|7634610177|7671710177|7673310177|7675410177|8505581100|8510851100|8511191100|8808751100|8866251100|8866271100|8896391100|9207931100|9208011100|9212751100|9212771100|9212791100|9212811100|9212831100|9212851100|9212871100|9212891100|9215521100|9217341100|9260571100|9260591100|9200301100|9209341100|9209361100|9209721100|7184270100|7289120114|7631910177|7632010177|9209681100|9209701100|457000009600|457100000013|457100000014|457100000023|457100000024|457100007200|457100034700|7170520100|7178042900|7184170110|7184270190|7184270230|7281620116|7281620117|7281620118|7282120136|7282120137|7283120185|7289120117|7289120157|7289120164|7289120188|7291727736|7293420156|7293720177|7295520135|7295520166|7299420123|7632110177|7632210177|7634710177|7634810177|7634910177|7635210177|8896331100|8896351100|8896371100|9200321100|9200341100|9200361100|9205831100|9212261100|7282120165</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3409,12 +3549,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3435,10 +3576,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="İZZET"/>
       <sheetName val="TEKLİF"/>
@@ -6557,7 +6694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF94ABC-17A7-4155-AB8E-F2609DBAA36D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z530"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17123,7 +17260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAAE4B4-287D-4140-8C5A-05B56D04A6C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z446"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31718,7 +31855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C4A705-747F-4A47-8C3A-C1517C3BF521}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31942,8 +32079,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718A2C2A-74F1-4973-AAA6-FB347C64E075}">
-  <dimension ref="A1:H5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -31953,7 +32090,7 @@
     <col min="5" max="8" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1067</v>
       </c>
@@ -31978,8 +32115,11 @@
       <c r="H1" s="1" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1075</v>
       </c>
@@ -32005,7 +32145,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1081</v>
       </c>
@@ -32031,7 +32171,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1087</v>
       </c>
@@ -32044,39 +32184,319 @@
       <c r="D4" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>1090</v>
       </c>
-      <c r="G4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>1092</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1094</v>
       </c>
       <c r="C5" s="3">
         <v>15000</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B6" t="s">
         <v>1097</v>
+      </c>
+      <c r="C6">
+        <v>5599</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C7">
+        <v>3349</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C8">
+        <v>7000</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C9">
+        <v>7000</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C10">
+        <v>2000</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C11">
+        <v>1999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C12">
+        <v>10990</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C13">
+        <v>15000</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C14">
+        <v>20000</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C15">
+        <v>3200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C16">
+        <v>7300</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C17">
+        <v>3000</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C18">
+        <v>1500</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C19">
+        <v>500</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
